--- a/data_extactor/batch_10_fa/trimmed/batch_0027_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0027_fa_trim.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | نگارش | شنیدن فعال | سخن گفتن</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | نگارش | گوش دادن فعال | سخن گفتن</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک کتبی | درک شفاهی | مرتب‌سازی اطلاعات | دید نزدیک | بیان کتبی | استدلال استقرایی | استدلال قیاسی</t>
+          <t>درک کتبی | درک شفاهی | ترتیب‌دهی اطلاعات | بینایی نزدیک | بیان کتبی | استدلال استقرایی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>تکنسین‌های شیمی | کاردان‌ها و تکنسین‌های مهندسی محیط‌زیست | متخصصان علوم زمین به‌جز آب‌زمین‌شناسان و جغرافیدانان | تکنسین‌های آب‌شناسی و هیدرولوژی | مهندسان معدن و زمین‌شناسی ازجمله مهندسان ایمنی معدن | مهندسان نفت | تکنسین‌های نقشه‌برداری و نقشه‌کشی</t>
+          <t>تکنسین‌های شیمی | کارشناسان و تکنسین‌های مهندسی محیط زیست | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | تکنسین‌های آب‌شناسی و هیدرولوژی | مهندسان معدن و زمین‌شناسی شامل مهندسان ایمنی معدن | مهندسان نفت | تکنسین‌های نقشه‌برداری و نقشه‌نگاری</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مهندسان عمران | کاردان‌ها و تکنسین‌های مهندسی محیط‌زیست | تکنسین‌های علوم و حفاظت محیط‌زیست ازجمله بهداشت محیط | کاردان‌ها و تکنسین‌های زمین‌شناسی به‌جز آب‌زمین‌شناسی | آب‌شناسان و هیدرولوژیست‌ها | متخصصان منابع آب | مهندسان آب و فاضلاب</t>
+          <t>مهندسان عمران | کارشناسان و تکنسین‌های مهندسی محیط زیست | تکنسین‌های علوم و بهداشت محیط زیست | کاردان‌ها و تکنسین‌های زمین‌شناسی به‌جز آب‌زمین‌شناسی | آب‌شناسان و هیدرولوژیست‌ها | کارشناسان و متخصصان مدیریت منابع آب | مهندسان آب و فاضلاب</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | یادگیری فعال | نگارش | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | یادگیری فعال | نگارش | سخن گفتن</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | مرتب‌سازی اطلاعات | درک شفاهی | درک کتبی | استدلال استقرایی | دید نزدیک | استدلال قیاسی</t>
+          <t>حساسیت به مسئله | ترتیب‌دهی اطلاعات | درک شفاهی | درک کتبی | استدلال استقرایی | بینایی نزدیک | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>کاردان‌ها و تکنسین‌های کالیبراسیون | کاردان‌ها و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکاران تجهیزات الکتریکی و الکترونیکی نیروگاه، پست برق و رله | مهندسان هسته‌ای | تکنسین‌های پایش و حفاظت پرتوی | اپراتورهای رآکتور هسته‌ای | اپراتورهای نیروگاه برق</t>
+          <t>تکنسین‌ها و کارشناسان فنی کالیبراسیون | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکار تجهیزات الکتریکی نیروگاه، پست برق و رله | مهندسان هسته‌ای | تکنسین‌های پایش و حفاظت پرتوی | اپراتورهای رآکتور نیروگاه هسته‌ای | اپراتورهای نیروگاه برق</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | نظارت | درک مطلب | سخن گفتن | ریاضیات | علوم | راهبردهای یادگیری | نگارش | یادگیری فعال</t>
+          <t>گوش دادن فعال | تفکر انتقادی | نظارت | درک مطلب | سخن گفتن | ریاضیات | علوم | راهبردهای یادگیری | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | دید نزدیک | مرتب‌سازی اطلاعات</t>
+          <t>حساسیت به مسئله | درک شفاهی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تکنسین‌های شیمی | تکنسین‌های علوم و حفاظت محیط‌زیست ازجمله بهداشت محیط | مهندسان ایمنی و بهداشت به‌جز مهندسان و بازرسان ایمنی معدن | متخصصان آزمون‌های غیرمخرب (NDT) | مهندسان هسته‌ای | کارشناسان فناوری پزشکی هسته‌ای | تکنسین‌های هسته‌ای</t>
+          <t>تکنسین‌های شیمی | تکنسین‌های علوم و بهداشت محیط زیست | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | متخصصان آزمون‌های غیرمخرب NDT | مهندسان هسته‌ای | کارشناسان و تکنسین‌های پزشکی هسته‌ای | تکنسین‌های هسته‌ای</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | نگارش | تفکر انتقادی | سخن گفتن | علوم | ریاضیات | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | نگارش | تفکر انتقادی | سخن گفتن | علوم | ریاضیات | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | رایانه و الکترونیک | اداری | ریاضیات | خدمات مشتریان و خدمات فردی</t>
+          <t>زبان انگلیسی | رایانه و الکترونیک | اداری | ریاضیات | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | مرتب‌سازی اطلاعات | استدلال قیاسی | استدلال استقرایی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>دانشمندان داده | هماهنگ‌کنندگان و کارشناسان برنامه‌ریزی آموزشی | مصاحبه‌گران به‌جز مصاحبه‌گران اعتبارسنجی و وام | تحلیل‌گران مدیریت و بهبود فرایند | جامعه‌شناسان | کارشناسان آمار | پژوهشگران و تحلیل‌گران نظرسنجی</t>
+          <t>دانشمندان داده | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | پرسشگران و مصاحبه‌گران، به جز امور وام و تعیین صلاحیت | کارشناسان تحلیل مدیریت و روش‌ها | جامعه‌شناسان | کارشناسان آمار | پژوهشگران پیمایشی و افکارسنجی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | نظارت | راهبردهای یادگیری | یادگیری فعال | نگارش</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | نظارت | راهبردهای یادگیری | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | حقوق و مقررات دولتی | جغرافیا | ریاضیات | زیست‌شناسی | مکانیک</t>
+          <t>ایمنی و امنیت عمومی | قانون و دولت | جغرافیا | ریاضیات | زیست‌شناسی | مکانیک</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>مرتب‌سازی اطلاعات | درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | دید دور</t>
+          <t>ترتیب‌دهی اطلاعات | درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بینایی دور</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>تکنسین‌های کشاورزی | دانشمندان حفاظت منابع طبیعی | سرپرستان رده‌اول کارگران کشاورزی، صیادی و جنگل‌داری | بازرسان و کارشناسان پیشگیری و اطفای حریق جنگل | کارگران جنگل‌داری و حفاظت از منابع طبیعی | کارشناسان و مهندسان جنگل‌داری | کارشناسان مدیریت مرتع و آبخیز</t>
+          <t>تکنسین‌های کشاورزی | دانشمندان حفاظت از منابع طبیعی | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | بازرسان و کارشناسان پیشگیری از حریق جنگل | کارگران جنگل‌داری و حفاظت از منابع طبیعی | کارشناسان جنگل‌داری و جنگل‌بانان | مدیران و کارشناسان مدیریت مراتع</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | نگارش | شنیدن فعال | درک مطلب | یادگیری فعال | نظارت | علوم | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | نگارش | گوش دادن فعال | درک مطلب | یادگیری فعال | نظارت | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>حقوق و مقررات دولتی | ایمنی و امنیت عمومی | رایانه و الکترونیک | مدیریت و امور اداری | شیمی | زیست‌شناسی</t>
+          <t>قانون و دولت | ایمنی و امنیت عمومی | رایانه و الکترونیک | مدیریت و اداره | شیمی | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال استقرایی | حساسیت به مسئله</t>
+          <t>بینایی نزدیک | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال استقرایی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تکنسین‌های زیست‌شناسی | بازرسان مرگ مشکوک و کارشناسان پزشکی قانونی | کارآگاهان و بازرسان کشف جرم | تحلیل‌گران جرایم دیجیتال و فارنزیک رایانه‌ای | کاردان‌ها و تکنسین‌های آزمایشگاه‌های پزشکی و بالینی | پزشکان متخصص آسیب‌شناسی (پاتولوژیست) | افسران تشخیص هویت و ثبت سوابق پلیس</t>
+          <t>تکنسین‌های علوم زیستی | پزشکان قانونی و بازرسان مرگ مشکوک | کارآگاهان و بازرسان جنایی | تحلیل‌گران جرم‌یابی دیجیتال و پاسخ به حوادث | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | پزشکان متخصص پاتولوژی | کارشناسان تشخیص هویت و ثبت سوابق پلیس</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تکنسین‌های زیست‌شناسی | تکنسین‌های شیمی | تکنسین‌های کشاورزی | تکنسین‌های علوم و حفاظت محیط‌زیست ازجمله بهداشت محیط | کاردان‌ها و تکنسین‌های زمین‌شناسی به‌جز آب‌زمین‌شناسی | تکنسین‌های آب‌شناسی و هیدرولوژی | کارشناسان تحلیل کنترل کیفیت</t>
+          <t>تکنسین‌های علوم زیستی | تکنسین‌های شیمی | تکنسین‌های کشاورزی | تکنسین‌های علوم و بهداشت محیط زیست | کاردان‌ها و تکنسین‌های زمین‌شناسی به‌جز آب‌زمین‌شناسی | تکنسین‌های آب‌شناسی و هیدرولوژی | کارشناسان تحلیل کنترل کیفیت</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | نظارت | شنیدن فعال | تفکر انتقادی | نگارش | سخن گفتن | یادگیری فعال | ریاضیات</t>
+          <t>درک مطلب | نظارت | گوش دادن فعال | تفکر انتقادی | نگارش | سخن گفتن | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک کتبی | درک شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی</t>
+          <t>بینایی نزدیک | درک کتبی | درک شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>کاردان‌ها و تکنسین‌های کالیبراسیون | تکنسین‌های شیمی | تکنسین‌های علوم و صنایع غذایی | کاردان‌ها و تکنسین‌های مهندسی صنایع | بازرسان، آزمون‌گران، درجه‌بندان، نمونه‌برداران و توزین‌کنندگان | مدیران سیستم‌های کنترل کیفیت | مهندسان اعتبارسنجی و صحه‌گذاری</t>
+          <t>تکنسین‌ها و کارشناسان فنی کالیبراسیون | تکنسین‌های شیمی | تکنسین‌های علوم و صنایع غذایی | کارشناسان و تکنسین‌های مهندسی صنایع | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | مدیران سیستم‌های کنترل کیفیت | مهندسان اعتبارسنجی و صحه‌گذاری</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | سخن گفتن | ریاضیات | شنیدن فعال | نظارت | نگارش | یادگیری فعال</t>
+          <t>تفکر انتقادی | درک مطلب | سخن گفتن | ریاضیات | گوش دادن فعال | نظارت | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>جغرافیا | رایانه و الکترونیک | ریاضیات | خدمات مشتریان و خدمات فردی | مهندسی و فناوری | تولید و فرآوری | زبان انگلیسی</t>
+          <t>جغرافیا | رایانه و الکترونیک | ریاضیات | خدمات مشتری و شخصی | مهندسی و فناوری | تولید و فرآوری | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | استدلال استقرایی | درک شفاهی | درک کتبی</t>
+          <t>استدلال قیاسی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | استدلال استقرایی | درک شفاهی | درک کتبی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>کاردان‌ها و تکنسین‌های کالیبراسیون | کارتوگراف‌ها و کارشناسان فتوگرامتری | نقشه‌برداران ژئودتیک | کاردان‌ها و تکنسین‌های سیستم اطلاعات جغرافیایی GIS | تکنسین‌های کشاورزی دقیق | دانشمندان و کارشناسان فناوری سنجش از دور | تکنسین‌های نقشه‌برداری و نقشه‌کشی</t>
+          <t>تکنسین‌ها و کارشناسان فنی کالیبراسیون | کارشناسان نقشه‌نگاری و فتوگرامتری | مهندسان نقشه‌برداری ژئودزی | تکنسین‌ها و کارشناسان سیستم‌های اطلاعات جغرافیایی GIS | تکنسین‌های کشاورزی دقیق | دانشمندان و فناوران سنجش از دور | تکنسین‌های نقشه‌برداری و نقشه‌نگاری</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
